--- a/Java24PhamThanhHuy Database Design.xlsx
+++ b/Java24PhamThanhHuy Database Design.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\JAVA24\3.Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82503390-C878-4A33-9133-960E422E0018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFB980B-1824-472E-B040-CFCEBFA954E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13110" yWindow="0" windowWidth="12580" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="63">
   <si>
     <t>MatHang</t>
   </si>
@@ -52,6 +63,168 @@
   </si>
   <si>
     <t>MauSac(s)</t>
+  </si>
+  <si>
+    <t>Nam</t>
+  </si>
+  <si>
+    <t>Nu</t>
+  </si>
+  <si>
+    <t>EmBe</t>
+  </si>
+  <si>
+    <t>AoThun</t>
+  </si>
+  <si>
+    <t>AoVest</t>
+  </si>
+  <si>
+    <t>QuanJean</t>
+  </si>
+  <si>
+    <t>QuanKaki</t>
+  </si>
+  <si>
+    <t>QuanTay</t>
+  </si>
+  <si>
+    <t>QuanDai</t>
+  </si>
+  <si>
+    <t>QuanShorts</t>
+  </si>
+  <si>
+    <t>TenMatHang</t>
+  </si>
+  <si>
+    <t>TenNSX</t>
+  </si>
+  <si>
+    <t>AoKhoac</t>
+  </si>
+  <si>
+    <t>Vay</t>
+  </si>
+  <si>
+    <t>QuanLegging</t>
+  </si>
+  <si>
+    <t>AoSoMiNganTay</t>
+  </si>
+  <si>
+    <t>DamNgan</t>
+  </si>
+  <si>
+    <t>DamDai</t>
+  </si>
+  <si>
+    <t>AoSoMiDaiTay</t>
+  </si>
+  <si>
+    <t>BabyBoy</t>
+  </si>
+  <si>
+    <t>BabyGirl</t>
+  </si>
+  <si>
+    <t>Boy</t>
+  </si>
+  <si>
+    <t>Girl</t>
+  </si>
+  <si>
+    <t>Yem</t>
+  </si>
+  <si>
+    <t>QuanSort</t>
+  </si>
+  <si>
+    <t>Jean</t>
+  </si>
+  <si>
+    <t>Kaki</t>
+  </si>
+  <si>
+    <t>AoThunNganTay</t>
+  </si>
+  <si>
+    <t>AoThunDaiTay</t>
+  </si>
+  <si>
+    <t>QuanDaiBabyBoi</t>
+  </si>
+  <si>
+    <t>BabyBoi</t>
+  </si>
+  <si>
+    <t>VayNgan</t>
+  </si>
+  <si>
+    <t>VayDai</t>
+  </si>
+  <si>
+    <t>Boi</t>
+  </si>
+  <si>
+    <t>DonHang</t>
+  </si>
+  <si>
+    <t>TenKH</t>
+  </si>
+  <si>
+    <t>DiaChi</t>
+  </si>
+  <si>
+    <t>SDT</t>
+  </si>
+  <si>
+    <t>LoaiHinhTT</t>
+  </si>
+  <si>
+    <t>Onl</t>
+  </si>
+  <si>
+    <t>COD</t>
+  </si>
+  <si>
+    <t>ThoiGian</t>
+  </si>
+  <si>
+    <t>SoLuong</t>
+  </si>
+  <si>
+    <t>TongTien</t>
+  </si>
+  <si>
+    <t>PhiVanChuyen</t>
+  </si>
+  <si>
+    <t>KhachHang</t>
+  </si>
+  <si>
+    <t>Mail</t>
+  </si>
+  <si>
+    <t>TinhTrangDonHang</t>
+  </si>
+  <si>
+    <t>MoiNhan</t>
+  </si>
+  <si>
+    <t>DaLayHang</t>
+  </si>
+  <si>
+    <t>DangGiao</t>
+  </si>
+  <si>
+    <t>DaGiao</t>
+  </si>
+  <si>
+    <t>HoanTra</t>
+  </si>
+  <si>
+    <t>NguoiGiao</t>
   </si>
 </sst>
 </file>
@@ -110,9 +283,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,180 +577,609 @@
     <row r="3" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="6" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="7" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="11" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="12" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
     </row>
     <row r="13" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
     </row>
     <row r="15" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+    </row>
+    <row r="16" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+    </row>
+    <row r="17" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+    </row>
+    <row r="18" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+    </row>
+    <row r="19" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+    </row>
+    <row r="20" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+    </row>
+    <row r="21" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+    </row>
+    <row r="22" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+    </row>
+    <row r="23" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+    </row>
+    <row r="24" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+    </row>
+    <row r="25" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+    </row>
+    <row r="26" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+    </row>
+    <row r="27" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="34" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="35" ht="22" customHeight="1" x14ac:dyDescent="0.35"/>
